--- a/Project5815_D. Cusco(2025).xlsx
+++ b/Project5815_D. Cusco(2025).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\neotrans\inst\matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2E1395-C02E-4F69-B455-ACA7E11204BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E977B88-D085-4390-AED9-72D5E1CB46A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E776B1BE-8EA0-4BBA-8DCD-3B926306C2C9}"/>
   </bookViews>
@@ -141,56 +141,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{EC5313F3-F762-49F2-865C-A0C2AA0A7D2F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dominic Cusco:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-14A: Presence of axial border furrow along L1
-14B: Distinctness of axial border furrow along L1</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{58E33A39-47FC-4A64-94B0-EE67853970CC}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dominic Cusco:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-15A: Presence of palpebral border furrow
-15B: Distinctness of palpebral border furrow</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="B18" authorId="0" shapeId="0" xr:uid="{26BB44A6-389C-4F39-B35E-5D75FCC8319F}">
       <text>
         <r>
@@ -321,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="45">
   <si>
     <t>Charlabels</t>
   </si>
@@ -449,14 +399,20 @@
     <t>NT?;0=0-;1=11;2=12;3=13;4=14</t>
   </si>
   <si>
-    <t>NT?;0=0-;1=11;2=12;3=13</t>
+    <t>NT2;0=0-;1=11;2=12</t>
+  </si>
+  <si>
+    <t>NT3;0=0-;1=11;2=12</t>
+  </si>
+  <si>
+    <t>NT3;0=0-;1=11;2=12;3=13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,6 +461,12 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -526,12 +488,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -994,6 +957,9 @@
       <c r="B9" t="s">
         <v>40</v>
       </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -1002,13 +968,19 @@
       <c r="B10" t="s">
         <v>39</v>
       </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1032,6 +1004,9 @@
       <c r="B13" t="s">
         <v>41</v>
       </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -1052,7 +1027,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1060,7 +1041,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1084,6 +1071,9 @@
       <c r="B18" t="s">
         <v>39</v>
       </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -1132,7 +1122,10 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1140,7 +1133,10 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1176,7 +1172,10 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1198,7 +1197,10 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
